--- a/LISTAS_ORDENADAS/MI/Sogas Varillas Cables/SOGA MULTIFILAMENTO.xlsx
+++ b/LISTAS_ORDENADAS/MI/Sogas Varillas Cables/SOGA MULTIFILAMENTO.xlsx
@@ -761,14 +761,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45203.55241929865</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+        <v>45266</v>
+      </c>
+    </row>
     <row r="7" ht="22.5" customHeight="1" s="18">
       <c r="A7" s="20" t="inlineStr">
         <is>
@@ -996,23 +991,6 @@
     <row r="22" ht="19.5" customHeight="1" s="18">
       <c r="G22" s="16" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
